--- a/artfynd/A 49016-2025 artfynd.xlsx
+++ b/artfynd/A 49016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130047615</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49016-2025 artfynd.xlsx
+++ b/artfynd/A 49016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130047615</v>
       </c>
       <c r="B2" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49016-2025 artfynd.xlsx
+++ b/artfynd/A 49016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130047615</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49016-2025 artfynd.xlsx
+++ b/artfynd/A 49016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130047615</v>
       </c>
       <c r="B2" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49016-2025 artfynd.xlsx
+++ b/artfynd/A 49016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130047615</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49016-2025 artfynd.xlsx
+++ b/artfynd/A 49016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130047615</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
